--- a/Documentacion Final/Requisitos - DilanMotos/Casos_Prueba V2.xlsx
+++ b/Documentacion Final/Requisitos - DilanMotos/Casos_Prueba V2.xlsx
@@ -1,46 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aprendiz\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D137D8C9-4C6F-458C-B420-2EE90DC66B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla" sheetId="1" r:id="rId1"/>
     <sheet name="Ejemplo" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="hFNZ1bas3awcInyRVQ+uKe6zLBIks7GPmqO2B+ZvBe8="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="513">
   <si>
     <t>RF</t>
   </si>
@@ -668,20 +643,6 @@
     <t>CP-010-03</t>
   </si>
   <si>
-    <t>Validar el comportamiento del sistema cuando el token 
-JWT ha expirado</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión
-2.Simular expiración del token (o esperar expiración)
-3.Estar en un submódulo
-4.Hacer clic en “Volver”</t>
-  </si>
-  <si>
-    <t>El sistema detecta el token inválido y redirige a la pantalla 
-de login mostrando error 401.</t>
-  </si>
-  <si>
     <t>CP-010-04</t>
   </si>
   <si>
@@ -698,9 +659,6 @@
 igual que el botón “Volver”</t>
   </si>
   <si>
-    <t>CP-010-05</t>
-  </si>
-  <si>
     <t>Validar el comportamiento ante error de conexión al cargar 
 datos del panel principal</t>
   </si>
@@ -718,85 +676,13 @@
     <t>CP-011-01</t>
   </si>
   <si>
-    <t>Validar que el usuario accede correctamente al módulo de 
-recomendaciones teniendo una motocicleta registrada</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión en el sistema
-2.Verificar que el usuario tenga al menos una moto registrada
-3.Hacer clic en “Asistente IA” o “Ver recomendaciones de la IA”
-4.Esperar carga del módulo</t>
-  </si>
-  <si>
-    <t>El sistema valida la sesión, detecta el vehículo y carga la 
-vista con recomendaciones personalizadas</t>
-  </si>
-  <si>
     <t>CP-011-02</t>
   </si>
   <si>
-    <t>Validar que el sistema impida el acceso si no hay vehículo 
-registrado</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión con un usuario sin motos registradas
-2.Hacer clic en “Asistente IA”
-3.Observar respuesta del sistema</t>
-  </si>
-  <si>
-    <t>El sistema muestra mensaje:
-“Para recibir recomendaciones precisas con IA, primero 
-debes registrar tu motocicleta.”</t>
-  </si>
-  <si>
     <t>CP-011-03</t>
   </si>
   <si>
-    <t>Validar que el acceso al módulo IA requiere sesión activa</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión
-2.Expirar o invalidar el token
-3.Intentar acceder al módulo IA
-4.Observar comportamiento</t>
-  </si>
-  <si>
-    <t>El sistema bloquea el acceso y redirige al login</t>
-  </si>
-  <si>
     <t>CP-011-04</t>
-  </si>
-  <si>
-    <t>Validar el manejo de errores cuando el motor de IA no 
-responde</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión con usuario con moto registrada
-2.Simular caída del servicio de IA
-3.Acceder al módulo IA
-4.Observar respuesta</t>
-  </si>
-  <si>
-    <t>El sistema muestra:
-“Servicio de recomendaciones en mantenimiento temporal. Puede consultar el catálogo general.”</t>
-  </si>
-  <si>
-    <t>CP-011-05</t>
-  </si>
-  <si>
-    <t>Validar que el módulo carga correctamente y permite 
-interacción (chat IA)</t>
-  </si>
-  <si>
-    <t>1.Iniciar sesión
-2.Acceder al módulo IA con moto registrada
-3.Esperar carga de la vista
-4.Interactuar con el chat IA</t>
-  </si>
-  <si>
-    <t>El módulo carga sin errores
-Se muestra la recomendación inicial
-El usuario puede interactuar con el chat sin bloqueos</t>
   </si>
   <si>
     <t>CP-012-01</t>
@@ -1976,16 +1862,70 @@
 Subtotal
 Estado</t>
   </si>
+  <si>
+    <t>Validar el acceso y carga inicial de recomendaciones según la motocicleta registrada</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión con un usuario activo.
+2. Acceder al módulo 'Asistente IA' / 'Recomendaciones'.
+3. Verificar la detección de la motocicleta registrada.
+4. Observar la vista de recomendaciones.</t>
+  </si>
+  <si>
+    <t>El sistema detecta automáticamente la motocicleta asociada al usuario y genera la lista inicial de recomendaciones de repuestos y mantenimiento personalizadas.</t>
+  </si>
+  <si>
+    <t>Validar la precisión de las recomendaciones en el chat de IA ante consultas de repuestos específicos</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión y acceder al módulo de IA.
+2. Enviar una consulta en el chat (ej. '¿Qué aceite y kit de arrastre requiere mi moto?').
+3. Esperar la respuesta del motor de IA.</t>
+  </si>
+  <si>
+    <t>El asistente de IA responde indicando repuestos e insumos específicos (viscosidad, marca, relación) compatibles con la ficha técnica del vehículo del usuario.</t>
+  </si>
+  <si>
+    <t>Validar que el acceso al módulo de IA requiere autenticación y sesión activa</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión en el sistema.
+2. Simular la expiración o invalidación del token JWT de sesión.
+3. Intentar acceder o enviar una solicitud al módulo IA.
+4. Observar la respuesta del sistema.</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la petición, no consulta la API de IA y redirige al usuario a la vista de Login mostrando un mensaje de sesión expirada.</t>
+  </si>
+  <si>
+    <t>La IA actualiza dinámicamente el contexto técnico al vehículo seleccionado y muestra repuestos específicos correspondientes a la nueva moto.</t>
+  </si>
+  <si>
+    <t>1. Iniciar sesión con un usuario que tiene registrada una motocicleta diferente a esa.
+2. Acceder al módulo IA y cambiar la moto activa seleccionada.
+3. Solicitar una nueva recomendación de repuestos.
+4. Verificar la respuesta generada.</t>
+  </si>
+  <si>
+    <t>Validar la actualización de recomendaciones al cambiar la motocicleta.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2006,8 +1946,13 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2032,8 +1977,14 @@
         <bgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2041,49 +1992,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2286,8 +2263,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E998"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -2678,7 +2655,7 @@
         <v>106</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>107</v>
@@ -2801,13 +2778,13 @@
         <v>140</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -2885,10 +2862,10 @@
         <v>161</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>163</v>
@@ -2940,21 +2917,21 @@
       <c r="A47" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>176</v>
+      <c r="B47" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B48" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C48" s="6" t="s">
@@ -2965,1154 +2942,1128 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="B50" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="B51" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+      <c r="B52" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D53" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+    <row r="54" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B54" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D54" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
+    <row r="55" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C55" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D55" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
+    <row r="56" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B56" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C56" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B61" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C61" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D61" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+    <row r="62" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C62" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
+    <row r="63" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B63" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C63" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D63" s="6" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
+    <row r="64" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D64" s="6" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
+    <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D65" s="6" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+    <row r="66" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C66" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D66" s="6" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+    <row r="67" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B67" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C67" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D67" s="6" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="120" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
+    <row r="68" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C68" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D68" s="6" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B72" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C72" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D72" s="6" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+    <row r="73" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B73" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C73" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A71" s="5" t="s">
+      <c r="C74" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="D74" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="C71" s="6" t="s">
+    </row>
+    <row r="75" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="B75" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A72" s="5" t="s">
+      <c r="C75" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="D75" s="6" t="s">
         <v>276</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A73" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C82" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D82" s="6" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A81" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>323</v>
+        <v>310</v>
+      </c>
+      <c r="C84" t="s">
+        <v>311</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B89" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D89" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="D86" s="6" t="s">
+    </row>
+    <row r="90" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A87" s="5" t="s">
+      <c r="B90" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="C90" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="D90" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A90" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>109</v>
+        <v>337</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>357</v>
+        <v>344</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>361</v>
+        <v>290</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>366</v>
+        <v>351</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B99" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C96" s="6" t="s">
+      <c r="C99" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D99" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="5" t="s">
+    <row r="100" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B100" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C100" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D100" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
+    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B101" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C101" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D101" s="5" t="s">
         <v>378</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B105" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C105" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D105" s="5" t="s">
         <v>394</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A105" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B109" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C109" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D109" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="5" t="s">
+    <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B110" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C110" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="D110" s="5" t="s">
         <v>414</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B114" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C114" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="D111" s="5" t="s">
+      <c r="D114" s="6" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
+    <row r="115" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B115" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="D115" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="D112" s="5" t="s">
+    </row>
+    <row r="116" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
+      <c r="B116" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="C116" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="D116" s="5" t="s">
         <v>437</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>117</v>
+        <v>439</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>453</v>
+        <v>440</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>461</v>
+        <v>294</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>463</v>
+        <v>298</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>467</v>
+        <v>453</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>454</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="B122" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C122" s="6" t="s">
+    </row>
+    <row r="126" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="B126" s="5" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="5" t="s">
+      <c r="C126" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="D126" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="6" t="s">
+    </row>
+    <row r="127" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="D123" s="5" t="s">
+      <c r="B127" s="5" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="5" t="s">
+      <c r="C127" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="D127" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A125" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A126" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4965,20 +4916,18 @@
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4991,7 +4940,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5013,23 +4962,23 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="4" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D4" s="8"/>
     </row>
@@ -5037,7 +4986,7 @@
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="4" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="D5" s="8"/>
     </row>
@@ -5045,7 +4994,7 @@
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="4" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="D6" s="8"/>
     </row>
@@ -5053,29 +5002,29 @@
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="4" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="4" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D9" s="8"/>
     </row>
@@ -5083,7 +5032,7 @@
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="D10" s="8"/>
     </row>
